--- a/Result/profitability/4736.xlsx
+++ b/Result/profitability/4736.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM71"/>
+  <dimension ref="A1:AM72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>4.78</v>
       </c>
       <c r="M2" t="n">
-        <v>3.4975</v>
+        <v>5.07625</v>
       </c>
       <c r="N2" t="n">
-        <v>46.7</v>
+        <v>45.90875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,13 +780,13 @@
         <v>3.6</v>
       </c>
       <c r="M3" t="n">
-        <v>3.81875</v>
+        <v>5.01875</v>
       </c>
       <c r="N3" t="n">
-        <v>45.32875</v>
+        <v>44.63625</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>5.86</v>
       </c>
       <c r="M4" t="n">
-        <v>4.04375</v>
+        <v>5.77125</v>
       </c>
       <c r="N4" t="n">
-        <v>45.04</v>
+        <v>44.18625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -923,7 +923,7 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" t="n">
         <v>98.2</v>
@@ -1018,10 +1018,10 @@
         <v>1.41</v>
       </c>
       <c r="M5" t="n">
-        <v>4.239999999999999</v>
+        <v>5.335</v>
       </c>
       <c r="N5" t="n">
-        <v>45.3175</v>
+        <v>43.48625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1033,7 +1033,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>2.13</v>
       </c>
       <c r="M6" t="n">
-        <v>3.89375</v>
+        <v>4.7975</v>
       </c>
       <c r="N6" t="n">
-        <v>43.4525</v>
+        <v>43.64875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>3.17625</v>
+        <v>4.39</v>
       </c>
       <c r="N7" t="n">
-        <v>43.535</v>
+        <v>43.81125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.8</v>
       </c>
       <c r="M8" t="n">
-        <v>2.7825</v>
+        <v>4.11625</v>
       </c>
       <c r="N8" t="n">
-        <v>42.5975</v>
+        <v>41.58625000000001</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9445,6 +9445,133 @@
       </c>
       <c r="AM71" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>4736</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>1048</v>
+      </c>
+      <c r="D72" t="n">
+        <v>614</v>
+      </c>
+      <c r="E72" t="n">
+        <v>434</v>
+      </c>
+      <c r="F72" t="n">
+        <v>41.41</v>
+      </c>
+      <c r="G72" t="n">
+        <v>142</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>13.54%</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>1211</v>
+      </c>
+      <c r="J72" t="n">
+        <v>1353</v>
+      </c>
+      <c r="K72" t="n">
+        <v>1290</v>
+      </c>
+      <c r="L72" t="n">
+        <v>13.66</v>
+      </c>
+      <c r="M72" t="n">
+        <v>4.6075</v>
+      </c>
+      <c r="N72" t="n">
+        <v>46.1175</v>
+      </c>
+      <c r="O72" t="n">
+        <v>1</v>
+      </c>
+      <c r="P72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>1</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
+      </c>
+      <c r="V72" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W72" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="X72" t="n">
+        <v>3.568561872909699</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>-8.090000000000003</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>-0.1634343434343435</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>1.787755102040816</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>-14.65000000000001</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>-0.2613271494826972</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK72" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL72" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM72" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
